--- a/Design/Excel/ET/Datas/Product/GridItemConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/GridItemConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1394,7 +1394,167 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>煮锅</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>番茄蛋花汤</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>面包片</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>烤面包</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>盘</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Product/GridItemConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/GridItemConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1173,6 +1173,16 @@
           <t>AcceptedDefinitionIds</t>
         </is>
       </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Discardable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1205,6 +1215,16 @@
           <t>(list#sep=,),int</t>
         </is>
       </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1237,6 +1257,16 @@
           <t>AcceptedDefinitionIds</t>
         </is>
       </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>Discardable</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1269,6 +1299,14 @@
           <t/>
         </is>
       </c>
+      <c r="G4" s="0">
+        <v>1</v>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1301,6 +1339,14 @@
           <t/>
         </is>
       </c>
+      <c r="G5" s="0">
+        <v>1</v>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1333,6 +1379,14 @@
           <t/>
         </is>
       </c>
+      <c r="G6" s="0">
+        <v>1</v>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1365,6 +1419,14 @@
           <t/>
         </is>
       </c>
+      <c r="G7" s="0">
+        <v>2</v>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1394,7 +1456,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3,4,7</t>
+          <t>3,4,7,11</t>
+        </is>
+      </c>
+      <c r="G8" s="0">
+        <v>3</v>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -1429,6 +1499,14 @@
           <t>2,4</t>
         </is>
       </c>
+      <c r="G9" s="0">
+        <v>3</v>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1461,6 +1539,14 @@
           <t/>
         </is>
       </c>
+      <c r="G10" s="0">
+        <v>2</v>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1493,6 +1579,14 @@
           <t/>
         </is>
       </c>
+      <c r="G11" s="0">
+        <v>1</v>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1525,6 +1619,14 @@
           <t/>
         </is>
       </c>
+      <c r="G12" s="0">
+        <v>1</v>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1555,6 +1657,150 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="0">
+        <v>3</v>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" s="0">
+        <v>2</v>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>番茄补给袋</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" s="0">
+        <v>3</v>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>鸡蛋补给袋</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="0">
+        <v>3</v>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>面包补给袋</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" s="0">
+        <v>3</v>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
         </is>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Product/GridItemConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/GridItemConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1183,6 +1183,21 @@
           <t>Discardable</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AllowsEmptyContainers</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Disposable</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>MenuVariant</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1225,6 +1240,21 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1267,6 +1297,21 @@
           <t>Discardable</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AllowsEmptyContainers</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Disposable</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>MenuVariant</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1307,6 +1352,21 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1347,6 +1407,21 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1387,6 +1462,21 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1427,6 +1517,21 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1467,6 +1572,21 @@
           <t>false</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1507,6 +1627,21 @@
           <t>false</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1547,6 +1682,21 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1587,6 +1737,21 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1627,6 +1792,21 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1667,6 +1847,21 @@
           <t>false</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1701,6 +1896,21 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1735,6 +1945,21 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1769,6 +1994,21 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1801,6 +2041,420 @@
       <c r="H17" s="0" t="inlineStr">
         <is>
           <t>true</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>橙块</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>果汁壶</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>鲜榨橙汁</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>一次性杯</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>橙子补给袋</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>空杯补给袋</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Product/GridItemConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/GridItemConfig.xlsx
@@ -1,693 +1,731 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnitProto" sheetId="1" r:id="R3c84dd27e2124d32"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnitProto" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
-    <x:numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </x:numFmts>
-  <x:fonts count="24">
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="9"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="9"/>
-      <x:color theme="1"/>
-      <x:name val="微软雅黑"/>
-    </x:font>
-    <x:font>
-      <x:sz val="12"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:u val="single"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:u val="single"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF800080"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFF0000"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="18"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="11"/>
-      <x:color rgb="FF7F7F7F"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="15"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="13"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F76"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F3F"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF006100"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C0006"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C6500"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="0"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:scheme val="minor"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="34">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF92D050"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFCC"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFCC99"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2F2F2"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA5A5A5"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFC6EFCE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFC7CE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFEB9C"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.59999"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.39998"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="9">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFB2B2B2"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="medium">
-        <x:color theme="4"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="medium">
-        <x:color theme="4" tint="0.49998"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:left>
-      <x:right style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:right>
-      <x:top style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="double">
-        <x:color rgb="FFFF8001"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top style="thin">
-        <x:color theme="4"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color theme="4"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="50">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <x:xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="7">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="50">
-    <x:cellStyle name="常规" xfId="0"/>
-    <x:cellStyle name="千位分隔" xfId="1"/>
-    <x:cellStyle name="货币" xfId="2"/>
-    <x:cellStyle name="百分比" xfId="3"/>
-    <x:cellStyle name="千位分隔[0]" xfId="4"/>
-    <x:cellStyle name="货币[0]" xfId="5"/>
-    <x:cellStyle name="超链接" xfId="6"/>
-    <x:cellStyle name="已访问的超链接" xfId="7"/>
-    <x:cellStyle name="注释" xfId="8"/>
-    <x:cellStyle name="警告文本" xfId="9"/>
-    <x:cellStyle name="标题" xfId="10"/>
-    <x:cellStyle name="解释性文本" xfId="11"/>
-    <x:cellStyle name="标题 1" xfId="12"/>
-    <x:cellStyle name="标题 2" xfId="13"/>
-    <x:cellStyle name="标题 3" xfId="14"/>
-    <x:cellStyle name="标题 4" xfId="15"/>
-    <x:cellStyle name="输入" xfId="16"/>
-    <x:cellStyle name="输出" xfId="17"/>
-    <x:cellStyle name="计算" xfId="18"/>
-    <x:cellStyle name="检查单元格" xfId="19"/>
-    <x:cellStyle name="链接单元格" xfId="20"/>
-    <x:cellStyle name="汇总" xfId="21"/>
-    <x:cellStyle name="好" xfId="22"/>
-    <x:cellStyle name="差" xfId="23"/>
-    <x:cellStyle name="适中" xfId="24"/>
-    <x:cellStyle name="强调文字颜色 1" xfId="25"/>
-    <x:cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
-    <x:cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
-    <x:cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
-    <x:cellStyle name="强调文字颜色 2" xfId="29"/>
-    <x:cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
-    <x:cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
-    <x:cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
-    <x:cellStyle name="强调文字颜色 3" xfId="33"/>
-    <x:cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
-    <x:cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
-    <x:cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
-    <x:cellStyle name="强调文字颜色 4" xfId="37"/>
-    <x:cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
-    <x:cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
-    <x:cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
-    <x:cellStyle name="强调文字颜色 5" xfId="41"/>
-    <x:cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
-    <x:cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
-    <x:cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
-    <x:cellStyle name="强调文字颜色 6" xfId="45"/>
-    <x:cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
-    <x:cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
-    <x:cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
-    <x:cellStyle name="常规 2" xfId="49"/>
-  </x:cellStyles>
-</x:styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <xfpb:bag type="Checkbox"/>
-  <xfpb:bag type="XFControls">
-    <xfpb:bagId k="CellControl">0</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplement">
-    <xfpb:bagId k="XFControls">1</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <xfpb:a k="MappedFeaturePropertyBags">
-      <xfpb:bagId>2</xfpb:bagId>
-    </xfpb:a>
-  </xfpb:bag>
-</xfpb:FeaturePropertyBags>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="24">
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="34">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="50">
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
+    <cellStyle name="常规 2" xfId="49"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -964,93 +1002,100 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L97"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+    <col width="21.125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12.75" customWidth="1" style="2" min="2" max="2"/>
+    <col width="12.625" customWidth="1" style="2" min="3" max="4"/>
+    <col width="15.125" customWidth="1" style="2" min="5" max="5"/>
+    <col width="9.625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="28.75" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11.75" customWidth="1" style="2" min="8" max="9"/>
+    <col width="6.75" customWidth="1" style="2" min="10" max="10"/>
+    <col width="9" customWidth="1" style="2" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">##var</t>
+          <t>##var</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kind</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ContainerCapacity</t>
+          <t>ContainerCapacity</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AcceptedDefinitionIds</t>
+          <t>AcceptedDefinitionIds</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Form</t>
+          <t>Form</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discardable</t>
+          <t>Discardable</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllowsEmptyContainers</t>
+          <t>AllowsEmptyContainers</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disposable</t>
+          <t>Disposable</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MenuVariant</t>
-        </is>
-      </c>
-      <c r="L1" t="str">
-        <v>ExclusiveDefinitionIds</v>
+          <t>MenuVariant</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ExclusiveDefinitionIds</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">##type</t>
+          <t>##type</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1060,12 +1105,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(list#sep=,),int</t>
+          <t>(list#sep=,),int</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1075,17 +1120,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bool</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bool</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bool</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1093,84 +1138,83 @@
           <t>ProductMenuVariant</t>
         </is>
       </c>
-      <c r="L2" t="str">
-        <v>(list#sep=,),int</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>(list#sep=,),int</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">##</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kind</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ContainerCapacity</t>
+          <t>ContainerCapacity</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AcceptedDefinitionIds</t>
+          <t>AcceptedDefinitionIds</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Form</t>
+          <t>Form</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discardable</t>
+          <t>Discardable</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AllowsEmptyContainers</t>
+          <t>AllowsEmptyContainers</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disposable</t>
+          <t>Disposable</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MenuVariant</t>
-        </is>
-      </c>
-      <c r="L3" t="str">
-        <v>必须独占容器的成品内容</v>
+          <t>MenuVariant</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>必须独占容器的成品内容</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄</t>
+          <t>番茄</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1180,12 +1224,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1195,17 +1234,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1215,19 +1254,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄块</t>
+          <t>番茄块</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1237,12 +1271,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1252,17 +1281,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1272,19 +1301,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">鸡蛋</t>
+          <t>鸡蛋</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1294,12 +1318,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1309,17 +1328,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1329,19 +1348,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">蛋液</t>
+          <t>蛋液</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1351,12 +1365,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1366,17 +1375,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1386,19 +1395,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">碗</t>
+          <t>碗</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1408,12 +1412,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3,4,7,11</t>
+          <t>3,4,7,11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1423,17 +1427,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1443,19 +1447,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">煮锅</t>
+          <t>煮锅</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1465,12 +1464,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2,4</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1480,17 +1479,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1500,19 +1499,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄蛋花汤</t>
+          <t>番茄蛋花汤</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1522,12 +1516,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1537,17 +1526,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1557,19 +1546,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">面包片</t>
+          <t>面包片</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1579,12 +1563,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1594,17 +1573,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1614,19 +1593,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">烤面包</t>
+          <t>烤面包</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1636,12 +1610,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1651,17 +1620,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1671,19 +1640,14 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">盘</t>
+          <t>盘</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1694,21 +1658,23 @@
       <c r="E13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" t="str">
-        <v>9,2,23,25,26,27,28,32,34,36,37,38,39</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>9,2,23,25,26,27,28,32,34,36,37,38,39</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H13" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6" t="b">
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
@@ -1716,22 +1682,19 @@
           <t>Basic</t>
         </is>
       </c>
-      <c r="L13" t="str">
-        <v>9,27,28,38,39</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>9,27,28,38,39</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>11</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">水</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1739,13 +1702,8 @@
           <t>Material</t>
         </is>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="E14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1754,17 +1712,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1774,17 +1732,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>12</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄补给袋</t>
+          <t>番茄补给袋</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1792,12 +1745,12 @@
           <t>Container</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1807,17 +1760,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1827,17 +1780,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>13</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">鸡蛋补给袋</t>
+          <t>鸡蛋补给袋</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1845,12 +1793,12 @@
           <t>Container</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1860,17 +1808,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1880,17 +1828,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">面包补给袋</t>
+          <t>面包补给袋</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1898,12 +1841,12 @@
           <t>Container</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1913,17 +1856,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1933,19 +1876,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">橙子</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1955,12 +1893,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1970,17 +1903,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1990,19 +1923,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">橙块</t>
+          <t>橙块</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2012,12 +1940,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2027,17 +1950,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2047,19 +1970,14 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">果汁壶</t>
+          <t>果汁壶</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2069,12 +1987,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2084,17 +2002,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2104,19 +2022,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">鲜榨橙汁</t>
+          <t>鲜榨橙汁</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2126,12 +2039,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t>0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2141,17 +2049,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2161,19 +2069,14 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">一次性杯</t>
+          <t>一次性杯</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2183,12 +2086,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2198,17 +2101,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2218,19 +2121,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">橙子补给袋</t>
+          <t>橙子补给袋</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2240,12 +2138,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2255,17 +2153,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2275,19 +2173,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">空杯补给袋</t>
+          <t>空杯补给袋</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2297,12 +2190,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2312,17 +2205,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2332,12 +2225,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str"/>
       <c r="B25" t="n">
         <v>22</v>
       </c>
-      <c r="C25" t="str">
-        <v>生菜</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>生菜</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2347,19 +2241,18 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
-      <c r="F25" t="str"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H25" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6" t="b">
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -2369,12 +2262,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str"/>
       <c r="B26" t="n">
         <v>23</v>
       </c>
-      <c r="C26" t="str">
-        <v>生菜片</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>生菜片</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2384,19 +2278,18 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="str"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H26" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I26" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6" t="b">
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -2406,12 +2299,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str"/>
       <c r="B27" t="n">
         <v>24</v>
       </c>
-      <c r="C27" t="str">
-        <v>黄瓜</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>黄瓜</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2421,19 +2315,18 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="F27" t="str"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H27" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I27" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6" t="b">
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
@@ -2443,12 +2336,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str"/>
       <c r="B28" t="n">
         <v>25</v>
       </c>
-      <c r="C28" t="str">
-        <v>黄瓜片</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>黄瓜片</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2458,19 +2352,18 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="str"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H28" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I28" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" s="6" t="b">
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -2480,12 +2373,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str"/>
       <c r="B29" t="n">
         <v>26</v>
       </c>
-      <c r="C29" t="str">
-        <v>芝士片</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>芝士片</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2495,19 +2389,18 @@
       <c r="E29" t="n">
         <v>0</v>
       </c>
-      <c r="F29" t="str"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H29" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I29" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" s="6" t="b">
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
@@ -2517,12 +2410,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str"/>
       <c r="B30" t="n">
         <v>27</v>
       </c>
-      <c r="C30" t="str">
-        <v>田园沙拉</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>田园沙拉</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2532,19 +2426,18 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" t="str"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H30" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I30" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" s="6" t="b">
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
@@ -2554,12 +2447,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str"/>
       <c r="B31" t="n">
         <v>28</v>
       </c>
-      <c r="C31" t="str">
-        <v>芝士蔬菜沙拉</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>芝士蔬菜沙拉</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2569,19 +2463,18 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="str"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H31" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I31" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" s="6" t="b">
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
@@ -2591,12 +2484,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str"/>
       <c r="B32" t="n">
         <v>29</v>
       </c>
-      <c r="C32" t="str">
-        <v>生菜补给袋</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>生菜补给袋</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2606,21 +2500,23 @@
       <c r="E32" t="n">
         <v>2</v>
       </c>
-      <c r="F32" t="str">
-        <v>22</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H32" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I32" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" s="6" t="b">
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
@@ -2630,12 +2526,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str"/>
       <c r="B33" t="n">
         <v>30</v>
       </c>
-      <c r="C33" t="str">
-        <v>黄瓜补给袋</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>黄瓜补给袋</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2645,21 +2542,23 @@
       <c r="E33" t="n">
         <v>2</v>
       </c>
-      <c r="F33" t="str">
-        <v>24</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H33" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I33" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" s="6" t="b">
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
@@ -2669,12 +2568,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str"/>
       <c r="B34" t="n">
         <v>31</v>
       </c>
-      <c r="C34" t="str">
-        <v>芝士补给袋</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>芝士补给袋</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2684,21 +2584,23 @@
       <c r="E34" t="n">
         <v>2</v>
       </c>
-      <c r="F34" t="str">
-        <v>26</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H34" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" s="6" t="b">
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
         <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
@@ -2708,12 +2610,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str"/>
       <c r="B35" t="n">
         <v>32</v>
       </c>
-      <c r="C35" t="str">
-        <v>汉堡面包</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>汉堡面包</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2723,19 +2626,18 @@
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35" t="str"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H35" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I35" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" s="6" t="b">
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
         <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
@@ -2743,15 +2645,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L35" t="str"/>
     </row>
     <row r="36">
-      <c r="A36" t="str"/>
       <c r="B36" t="n">
         <v>33</v>
       </c>
-      <c r="C36" t="str">
-        <v>生牛肉饼</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>生牛肉饼</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2761,19 +2663,18 @@
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="F36" t="str"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H36" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I36" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" s="6" t="b">
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
         <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -2781,15 +2682,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L36" t="str"/>
     </row>
     <row r="37">
-      <c r="A37" t="str"/>
       <c r="B37" t="n">
         <v>34</v>
       </c>
-      <c r="C37" t="str">
-        <v>熟牛肉饼</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>熟牛肉饼</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2799,19 +2700,18 @@
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="F37" t="str"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H37" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I37" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" s="6" t="b">
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
         <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -2819,15 +2719,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L37" t="str"/>
     </row>
     <row r="38">
-      <c r="A38" t="str"/>
       <c r="B38" t="n">
         <v>35</v>
       </c>
-      <c r="C38" t="str">
-        <v>生香肠</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>生香肠</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2837,19 +2737,18 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="str"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H38" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I38" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" s="6" t="b">
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
         <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -2857,15 +2756,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L38" t="str"/>
     </row>
     <row r="39">
-      <c r="A39" t="str"/>
       <c r="B39" t="n">
         <v>36</v>
       </c>
-      <c r="C39" t="str">
-        <v>熟香肠</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>熟香肠</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2875,19 +2774,18 @@
       <c r="E39" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="str"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H39" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I39" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" s="6" t="b">
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
         <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
@@ -2895,15 +2793,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L39" t="str"/>
     </row>
     <row r="40">
-      <c r="A40" t="str"/>
       <c r="B40" t="n">
         <v>37</v>
       </c>
-      <c r="C40" t="str">
-        <v>煎蛋</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>煎蛋</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2913,19 +2811,18 @@
       <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="str"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H40" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I40" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" s="6" t="b">
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
         <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
@@ -2933,15 +2830,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L40" t="str"/>
     </row>
     <row r="41">
-      <c r="A41" t="str"/>
       <c r="B41" t="n">
         <v>38</v>
       </c>
-      <c r="C41" t="str">
-        <v>经典牛肉汉堡</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>经典牛肉汉堡</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2951,19 +2848,18 @@
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="str"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H41" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I41" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" s="6" t="b">
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
         <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
@@ -2971,15 +2867,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L41" t="str"/>
     </row>
     <row r="42">
-      <c r="A42" t="str"/>
       <c r="B42" t="n">
         <v>39</v>
       </c>
-      <c r="C42" t="str">
-        <v>香肠鸡蛋早餐</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>香肠鸡蛋早餐</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2989,19 +2885,18 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="str"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H42" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I42" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" s="6" t="b">
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
@@ -3009,15 +2904,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L42" t="str"/>
     </row>
     <row r="43">
-      <c r="A43" t="str"/>
       <c r="B43" t="n">
         <v>40</v>
       </c>
-      <c r="C43" t="str">
-        <v>汉堡面包补给袋</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>汉堡面包补给袋</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3027,21 +2922,23 @@
       <c r="E43" t="n">
         <v>1</v>
       </c>
-      <c r="F43" t="str">
-        <v>32</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H43" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I43" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" s="6" t="b">
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
@@ -3049,15 +2946,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L43" t="str"/>
     </row>
     <row r="44">
-      <c r="A44" t="str"/>
       <c r="B44" t="n">
         <v>41</v>
       </c>
-      <c r="C44" t="str">
-        <v>牛肉饼补给袋</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>牛肉饼补给袋</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3067,21 +2964,23 @@
       <c r="E44" t="n">
         <v>1</v>
       </c>
-      <c r="F44" t="str">
-        <v>33</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H44" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I44" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" s="6" t="b">
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
         <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
@@ -3089,15 +2988,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L44" t="str"/>
     </row>
     <row r="45">
-      <c r="A45" t="str"/>
       <c r="B45" t="n">
         <v>42</v>
       </c>
-      <c r="C45" t="str">
-        <v>香肠补给袋</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>香肠补给袋</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3107,21 +3006,23 @@
       <c r="E45" t="n">
         <v>1</v>
       </c>
-      <c r="F45" t="str">
-        <v>35</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H45" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I45" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" s="6" t="b">
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
         <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
@@ -3129,15 +3030,15 @@
           <t>Hot</t>
         </is>
       </c>
-      <c r="L45" t="str"/>
     </row>
     <row r="46">
-      <c r="A46" t="str"/>
       <c r="B46" t="n">
         <v>43</v>
       </c>
-      <c r="C46" t="str">
-        <v>甜点预拌粉</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>甜点预拌粉</t>
+        </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3147,19 +3048,18 @@
       <c r="E46" t="n">
         <v>0</v>
       </c>
-      <c r="F46" t="str"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H46" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I46" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J46" s="6" t="b">
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
@@ -3167,15 +3067,15 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="L46" t="str"/>
     </row>
     <row r="47">
-      <c r="A47" t="str"/>
       <c r="B47" t="n">
         <v>44</v>
       </c>
-      <c r="C47" t="str">
-        <v>瓶装牛奶</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>瓶装牛奶</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3185,19 +3085,18 @@
       <c r="E47" t="n">
         <v>0</v>
       </c>
-      <c r="F47" t="str"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H47" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I47" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" s="6" t="b">
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
         <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
@@ -3205,15 +3104,15 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="L47" t="str"/>
     </row>
     <row r="48">
-      <c r="A48" t="str"/>
       <c r="B48" t="n">
         <v>45</v>
       </c>
-      <c r="C48" t="str">
-        <v>搅拌盆</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>搅拌盆</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3223,21 +3122,23 @@
       <c r="E48" t="n">
         <v>3</v>
       </c>
-      <c r="F48" t="str">
-        <v>43,3,44</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>43,3,44</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H48" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" s="6" t="b">
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
@@ -3245,15 +3146,15 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="L48" t="str"/>
     </row>
     <row r="49">
-      <c r="A49" t="str"/>
       <c r="B49" t="n">
         <v>46</v>
       </c>
-      <c r="C49" t="str">
-        <v>甜面糊</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>甜面糊</t>
+        </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3263,19 +3164,18 @@
       <c r="E49" t="n">
         <v>0</v>
       </c>
-      <c r="F49" t="str"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>Liquid</t>
         </is>
       </c>
-      <c r="H49" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I49" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J49" s="6" t="b">
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
@@ -3283,15 +3183,15 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="L49" t="str"/>
     </row>
     <row r="50">
-      <c r="A50" t="str"/>
       <c r="B50" t="n">
         <v>47</v>
       </c>
-      <c r="C50" t="str">
-        <v>小蛋糕模具</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>小蛋糕模具</t>
+        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3301,21 +3201,23 @@
       <c r="E50" t="n">
         <v>1</v>
       </c>
-      <c r="F50" t="str">
-        <v>46,48</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>46,48</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H50" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" s="6" t="b">
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
@@ -3323,17 +3225,20 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="L50" t="str">
-        <v>48</v>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str"/>
       <c r="B51" t="n">
         <v>48</v>
       </c>
-      <c r="C51" t="str">
-        <v>原味小蛋糕</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>原味小蛋糕</t>
+        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3343,19 +3248,18 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
-      <c r="F51" t="str"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H51" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I51" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" s="6" t="b">
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
@@ -3363,15 +3267,15 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="L51" t="str"/>
     </row>
     <row r="52">
-      <c r="A52" t="str"/>
       <c r="B52" t="n">
         <v>49</v>
       </c>
-      <c r="C52" t="str">
-        <v>甜品盘</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>甜品盘</t>
+        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3381,21 +3285,23 @@
       <c r="E52" t="n">
         <v>1</v>
       </c>
-      <c r="F52" t="str">
-        <v>48</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H52" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I52" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" s="6" t="b">
+      <c r="H52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="b">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
@@ -3403,17 +3309,20 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="L52" t="str">
-        <v>48</v>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str"/>
       <c r="B53" t="n">
         <v>50</v>
       </c>
-      <c r="C53" t="str">
-        <v>预拌粉补给袋</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>预拌粉补给袋</t>
+        </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3423,21 +3332,23 @@
       <c r="E53" t="n">
         <v>1</v>
       </c>
-      <c r="F53" t="str">
-        <v>43</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H53" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I53" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" s="6" t="b">
+      <c r="H53" t="b">
+        <v>1</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
@@ -3445,15 +3356,15 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="L53" t="str"/>
     </row>
     <row r="54">
-      <c r="A54" t="str"/>
       <c r="B54" t="n">
         <v>51</v>
       </c>
-      <c r="C54" t="str">
-        <v>牛奶补给盒</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>牛奶补给盒</t>
+        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3463,21 +3374,23 @@
       <c r="E54" t="n">
         <v>1</v>
       </c>
-      <c r="F54" t="str">
-        <v>44</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H54" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I54" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="b">
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
@@ -3485,15 +3398,15 @@
           <t>Dessert</t>
         </is>
       </c>
-      <c r="L54" t="str"/>
     </row>
     <row r="55">
-      <c r="A55" t="str"/>
       <c r="B55" t="n">
         <v>52</v>
       </c>
-      <c r="C55" t="str">
-        <v>咖啡豆</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>咖啡豆</t>
+        </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3503,19 +3416,18 @@
       <c r="E55" t="n">
         <v>0</v>
       </c>
-      <c r="F55" t="str"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H55" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I55" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="b">
+      <c r="H55" t="b">
+        <v>1</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
@@ -3523,15 +3435,15 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L55" t="str"/>
     </row>
     <row r="56">
-      <c r="A56" t="str"/>
       <c r="B56" t="n">
         <v>53</v>
       </c>
-      <c r="C56" t="str">
-        <v>咖啡粉</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>咖啡粉</t>
+        </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3541,19 +3453,18 @@
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="str"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
-      <c r="H56" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I56" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="b">
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
@@ -3561,15 +3472,15 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L56" t="str"/>
     </row>
     <row r="57">
-      <c r="A57" t="str"/>
       <c r="B57" t="n">
         <v>54</v>
       </c>
-      <c r="C57" t="str">
-        <v>咖啡接液壶</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>咖啡接液壶</t>
+        </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3579,21 +3490,23 @@
       <c r="E57" t="n">
         <v>1</v>
       </c>
-      <c r="F57" t="str">
-        <v>53</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H57" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" s="6" t="b">
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
@@ -3601,15 +3514,15 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L57" t="str"/>
     </row>
     <row r="58">
-      <c r="A58" t="str"/>
       <c r="B58" t="n">
         <v>55</v>
       </c>
-      <c r="C58" t="str">
-        <v>奶缸</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>奶缸</t>
+        </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3619,21 +3532,23 @@
       <c r="E58" t="n">
         <v>1</v>
       </c>
-      <c r="F58" t="str">
-        <v>44</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H58" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="b">
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
         <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
@@ -3641,15 +3556,15 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L58" t="str"/>
     </row>
     <row r="59">
-      <c r="A59" t="str"/>
       <c r="B59" t="n">
         <v>56</v>
       </c>
-      <c r="C59" t="str">
-        <v>浓缩咖啡液</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>浓缩咖啡液</t>
+        </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3659,19 +3574,18 @@
       <c r="E59" t="n">
         <v>0</v>
       </c>
-      <c r="F59" t="str"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>Liquid</t>
         </is>
       </c>
-      <c r="H59" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I59" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" s="6" t="b">
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="b">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
@@ -3679,15 +3593,15 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L59" t="str"/>
     </row>
     <row r="60">
-      <c r="A60" t="str"/>
       <c r="B60" t="n">
         <v>57</v>
       </c>
-      <c r="C60" t="str">
-        <v>热牛奶</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>热牛奶</t>
+        </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3697,19 +3611,18 @@
       <c r="E60" t="n">
         <v>0</v>
       </c>
-      <c r="F60" t="str"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>Liquid</t>
         </is>
       </c>
-      <c r="H60" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I60" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J60" s="6" t="b">
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
@@ -3717,15 +3630,15 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L60" t="str"/>
     </row>
     <row r="61">
-      <c r="A61" t="str"/>
       <c r="B61" t="n">
         <v>58</v>
       </c>
-      <c r="C61" t="str">
-        <v>奶泡</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>奶泡</t>
+        </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3735,19 +3648,18 @@
       <c r="E61" t="n">
         <v>0</v>
       </c>
-      <c r="F61" t="str"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>Liquid</t>
         </is>
       </c>
-      <c r="H61" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I61" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J61" s="6" t="b">
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
         <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
@@ -3755,15 +3667,15 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L61" t="str"/>
     </row>
     <row r="62">
-      <c r="A62" t="str"/>
       <c r="B62" t="n">
         <v>59</v>
       </c>
-      <c r="C62" t="str">
-        <v>热饮杯</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>热饮杯</t>
+        </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3773,21 +3685,23 @@
       <c r="E62" t="n">
         <v>3</v>
       </c>
-      <c r="F62" t="str">
-        <v>56,57,58,60,61</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>56,57,58,60,61,78</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H62" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I62" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J62" s="6" t="b">
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="inlineStr">
@@ -3795,17 +3709,20 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L62" t="str">
-        <v>56,60,61</v>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>56,60,61,78</t>
+        </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="str"/>
       <c r="B63" t="n">
         <v>60</v>
       </c>
-      <c r="C63" t="str">
-        <v>热拿铁</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>热拿铁</t>
+        </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3815,19 +3732,18 @@
       <c r="E63" t="n">
         <v>0</v>
       </c>
-      <c r="F63" t="str"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>Liquid</t>
         </is>
       </c>
-      <c r="H63" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I63" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J63" s="6" t="b">
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="b">
         <v>0</v>
       </c>
       <c r="K63" t="inlineStr">
@@ -3835,15 +3751,15 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L63" t="str"/>
     </row>
     <row r="64">
-      <c r="A64" t="str"/>
       <c r="B64" t="n">
         <v>61</v>
       </c>
-      <c r="C64" t="str">
-        <v>卡布奇诺</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>卡布奇诺</t>
+        </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3853,19 +3769,18 @@
       <c r="E64" t="n">
         <v>0</v>
       </c>
-      <c r="F64" t="str"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>Liquid</t>
         </is>
       </c>
-      <c r="H64" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I64" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" s="6" t="b">
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
         <v>0</v>
       </c>
       <c r="K64" t="inlineStr">
@@ -3873,15 +3788,15 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L64" t="str"/>
     </row>
     <row r="65">
-      <c r="A65" t="str"/>
       <c r="B65" t="n">
         <v>62</v>
       </c>
-      <c r="C65" t="str">
-        <v>咖啡豆补给袋</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>咖啡豆补给袋</t>
+        </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3891,21 +3806,23 @@
       <c r="E65" t="n">
         <v>1</v>
       </c>
-      <c r="F65" t="str">
-        <v>52</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H65" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I65" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J65" s="6" t="b">
+      <c r="H65" t="b">
+        <v>1</v>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65" t="b">
         <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
@@ -3913,15 +3830,15 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L65" t="str"/>
     </row>
     <row r="66">
-      <c r="A66" t="str"/>
       <c r="B66" t="n">
         <v>63</v>
       </c>
-      <c r="C66" t="str">
-        <v>热饮杯补给包</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>热饮杯补给包</t>
+        </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3931,21 +3848,23 @@
       <c r="E66" t="n">
         <v>3</v>
       </c>
-      <c r="F66" t="str">
-        <v>59</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>Container</t>
         </is>
       </c>
-      <c r="H66" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I66" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" s="6" t="b">
+      <c r="H66" t="b">
+        <v>1</v>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="b">
         <v>0</v>
       </c>
       <c r="K66" t="inlineStr">
@@ -3953,7 +3872,1238 @@
           <t>Cafe</t>
         </is>
       </c>
-      <c r="L66" t="str"/>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>64</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>洋葱</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H67" t="b">
+        <v>1</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>65</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>洋葱块</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H68" t="b">
+        <v>1</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>66</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>牛肉末</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H69" t="b">
+        <v>1</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>67</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>饺子皮</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H70" t="b">
+        <v>1</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>68</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>牛肉洋葱馅</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H71" t="b">
+        <v>1</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>69</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>未熟牛肉蒸饺</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H72" t="b">
+        <v>1</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>70</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>熟牛肉蒸饺</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H73" t="b">
+        <v>1</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>71</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>蒸食盘</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>72</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>拌馅盆</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>65,66,67,68,69</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H75" t="b">
+        <v>0</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>68,69</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>73</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>洋葱补给袋</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H76" t="b">
+        <v>1</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>74</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>牛肉末补给袋</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>75</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>饺子皮补给袋</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H78" t="b">
+        <v>1</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Steamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>76</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>热水</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Liquid</t>
+        </is>
+      </c>
+      <c r="H79" t="b">
+        <v>1</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>77</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>红茶叶</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H80" t="b">
+        <v>1</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>78</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>红茶底</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Liquid</t>
+        </is>
+      </c>
+      <c r="H81" t="b">
+        <v>1</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>79</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>生珍珠</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H82" t="b">
+        <v>1</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>80</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>熟珍珠</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>81</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>糖浆</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Liquid</t>
+        </is>
+      </c>
+      <c r="H84" t="b">
+        <v>1</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>82</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>奶茶基底</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Liquid</t>
+        </is>
+      </c>
+      <c r="H85" t="b">
+        <v>1</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>83</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>冰块</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="H86" t="b">
+        <v>1</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>84</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>透明冷饮杯</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>3</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>80,82,83,88,89</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H87" t="b">
+        <v>1</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="b">
+        <v>1</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>88,89</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>85</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>调饮壶</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>78,44,81</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H88" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>86</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>小料罐</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H89" t="b">
+        <v>0</v>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>87</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>泡茶桶</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>76,77</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H90" t="b">
+        <v>0</v>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>88</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>冰鲜奶茶</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Liquid</t>
+        </is>
+      </c>
+      <c r="H91" t="b">
+        <v>1</v>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>89</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>珍珠奶茶</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Liquid</t>
+        </is>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>90</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>红茶叶补给袋</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H93" t="b">
+        <v>1</v>
+      </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>91</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>生珍珠补给袋</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H94" t="b">
+        <v>1</v>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>92</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>糖浆补给包</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>93</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>冰块补给袋</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H96" t="b">
+        <v>1</v>
+      </c>
+      <c r="I96" t="b">
+        <v>0</v>
+      </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>94</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>冷饮杯补给包</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="H97" t="b">
+        <v>1</v>
+      </c>
+      <c r="I97" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
